--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\UIPath\Projects\MyEquityChartAnalyzer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UIPathRPA\Process\MyEquityChartAnalyzer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB24835B-D384-4FF9-9AEB-6460D3C076EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746F4627-B7F8-49F6-BD07-F9609EFD8684}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32235" yWindow="4560" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>Name</t>
   </si>
@@ -172,15 +172,9 @@
     <t>https://chartink.com/screener/gaurav-renko</t>
   </si>
   <si>
-    <t>Data Source=DESKTOP-TA0PFRN;Initial Catalog=MyEquityChartAnalyzer;Integrated Security=True;Encrypt=False</t>
-  </si>
-  <si>
     <t>RenkoChartScreenShot</t>
   </si>
   <si>
-    <t>I:\RPAData\MyEquityChartAnalyzer\RenkoChart\</t>
-  </si>
-  <si>
     <t>TradingViewLink</t>
   </si>
   <si>
@@ -188,6 +182,15 @@
   </si>
   <si>
     <t>RenkoChartFileSavePath</t>
+  </si>
+  <si>
+    <t>Data Source=.;Initial Catalog=MyEquityChartAnalyzer;Integrated Security=True;Encrypt=False</t>
+  </si>
+  <si>
+    <t>C:\UIPathRPA\RPAData\MyEquityChartAnalyzer\RenkoChart\</t>
+  </si>
+  <si>
+    <t>C:\UIPathRPA\RPAData\MyEquityChartAnalyzer\RenkoChart</t>
   </si>
 </sst>
 </file>
@@ -653,7 +656,7 @@
         <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -666,26 +669,26 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
